--- a/output/intraday/riepilogo_intraday_D2_2026-05-06.xlsx
+++ b/output/intraday/riepilogo_intraday_D2_2026-05-06.xlsx
@@ -714,7 +714,7 @@
         <v>7.09</v>
       </c>
       <c r="P2" t="n">
-        <v>2015919</v>
+        <v>2015980</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>5.27</v>
       </c>
       <c r="AG2" t="n">
-        <v>1336642</v>
+        <v>1336702</v>
       </c>
       <c r="AH2" t="n">
         <v>6.56</v>
@@ -780,7 +780,7 @@
         <v>5.27</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1495391</v>
+        <v>1495451</v>
       </c>
       <c r="AK2" t="n">
         <v>6.41</v>
@@ -792,7 +792,7 @@
         <v>5.27</v>
       </c>
       <c r="AN2" t="n">
-        <v>1586318</v>
+        <v>1586379</v>
       </c>
       <c r="AO2" t="n">
         <v>6.89</v>
@@ -804,7 +804,7 @@
         <v>5.27</v>
       </c>
       <c r="AR2" t="n">
-        <v>1639336</v>
+        <v>1639397</v>
       </c>
       <c r="AS2" t="n">
         <v>6.35</v>
@@ -816,7 +816,7 @@
         <v>5.27</v>
       </c>
       <c r="AV2" t="n">
-        <v>1784880</v>
+        <v>1784941</v>
       </c>
       <c r="AW2" t="n">
         <v>6.8</v>
@@ -873,7 +873,7 @@
         <v>1.1</v>
       </c>
       <c r="P3" t="n">
-        <v>3038052</v>
+        <v>4663660</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>1.03</v>
       </c>
       <c r="AN3" t="n">
-        <v>2443047</v>
+        <v>4068655</v>
       </c>
       <c r="AO3" t="n">
         <v>1.08</v>
@@ -963,7 +963,7 @@
         <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>2543611</v>
+        <v>4169219</v>
       </c>
       <c r="AS3" t="n">
         <v>1.13</v>
@@ -975,7 +975,7 @@
         <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>2831839</v>
+        <v>4457447</v>
       </c>
       <c r="AW3" t="n">
         <v>1.14</v>
@@ -1032,7 +1032,7 @@
         <v>6.85</v>
       </c>
       <c r="P4" t="n">
-        <v>16837462</v>
+        <v>41622729</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>4.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>13426079</v>
+        <v>25108362</v>
       </c>
       <c r="AW4" t="n">
         <v>8.52</v>
@@ -1191,7 +1191,7 @@
         <v>14.24</v>
       </c>
       <c r="P5" t="n">
-        <v>535302</v>
+        <v>536078</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>13.87</v>
       </c>
       <c r="AV5" t="n">
-        <v>360126</v>
+        <v>360596</v>
       </c>
       <c r="AW5" t="n">
         <v>14.12</v>

--- a/output/intraday/riepilogo_intraday_D2_2026-05-06.xlsx
+++ b/output/intraday/riepilogo_intraday_D2_2026-05-06.xlsx
@@ -714,7 +714,7 @@
         <v>7.09</v>
       </c>
       <c r="P2" t="n">
-        <v>2015980</v>
+        <v>2015919</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>5.27</v>
       </c>
       <c r="AG2" t="n">
-        <v>1336702</v>
+        <v>1336642</v>
       </c>
       <c r="AH2" t="n">
         <v>6.56</v>
@@ -780,7 +780,7 @@
         <v>5.27</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1495451</v>
+        <v>1495391</v>
       </c>
       <c r="AK2" t="n">
         <v>6.41</v>
@@ -792,7 +792,7 @@
         <v>5.27</v>
       </c>
       <c r="AN2" t="n">
-        <v>1586379</v>
+        <v>1586318</v>
       </c>
       <c r="AO2" t="n">
         <v>6.89</v>
@@ -804,7 +804,7 @@
         <v>5.27</v>
       </c>
       <c r="AR2" t="n">
-        <v>1639397</v>
+        <v>1639336</v>
       </c>
       <c r="AS2" t="n">
         <v>6.35</v>
@@ -816,7 +816,7 @@
         <v>5.27</v>
       </c>
       <c r="AV2" t="n">
-        <v>1784941</v>
+        <v>1784880</v>
       </c>
       <c r="AW2" t="n">
         <v>6.8</v>
@@ -873,7 +873,7 @@
         <v>1.1</v>
       </c>
       <c r="P3" t="n">
-        <v>4663660</v>
+        <v>3038052</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>1.03</v>
       </c>
       <c r="AN3" t="n">
-        <v>4068655</v>
+        <v>2443047</v>
       </c>
       <c r="AO3" t="n">
         <v>1.08</v>
@@ -963,7 +963,7 @@
         <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>4169219</v>
+        <v>2543611</v>
       </c>
       <c r="AS3" t="n">
         <v>1.13</v>
@@ -975,7 +975,7 @@
         <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>4457447</v>
+        <v>2831839</v>
       </c>
       <c r="AW3" t="n">
         <v>1.14</v>
@@ -1032,7 +1032,7 @@
         <v>6.85</v>
       </c>
       <c r="P4" t="n">
-        <v>41622729</v>
+        <v>16837462</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>4.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>25108362</v>
+        <v>13426079</v>
       </c>
       <c r="AW4" t="n">
         <v>8.52</v>
@@ -1191,7 +1191,7 @@
         <v>14.24</v>
       </c>
       <c r="P5" t="n">
-        <v>536078</v>
+        <v>535302</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>13.87</v>
       </c>
       <c r="AV5" t="n">
-        <v>360596</v>
+        <v>360126</v>
       </c>
       <c r="AW5" t="n">
         <v>14.12</v>
